--- a/TestData/PurchaseData-v2.xlsx
+++ b/TestData/PurchaseData-v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teste\Titan-Mobile-Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E31C17E-A22F-4A12-933D-69E05ADA7199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E24C68-F72C-40F1-BB25-91618527B4E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{42D689F5-8BC2-464B-8241-B0624ACD5F18}"/>
   </bookViews>
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="30">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -567,22 +570,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1BECAA-E7C3-4729-9704-A408DC33D20C}">
-  <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="15.109375" customWidth="1"/>
-    <col min="8" max="8" width="23.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,240 +620,157 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="12" t="s">
-        <v>27</v>
+      <c r="D2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="K2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="K5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="12"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D14" s="8"/>
+      <c r="I14" s="9"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D15" s="9"/>
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D16" s="8"/>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D16" s="9"/>
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D17" s="9"/>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D17" s="10"/>
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D18" s="9"/>
-      <c r="I18" s="9"/>
-    </row>
-    <row r="19" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="10"/>
+    </row>
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D19" s="10"/>
-      <c r="I19" s="9"/>
-    </row>
-    <row r="20" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D20" s="9"/>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D21" s="10"/>
-    </row>
-    <row r="22" spans="4:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I20" s="9"/>
+    </row>
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D21" s="8"/>
+      <c r="I21" s="9"/>
+    </row>
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D22" s="8"/>
       <c r="I22" s="9"/>
     </row>
-    <row r="23" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D23" s="8"/>
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D24" s="8"/>
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D24" s="10"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D25" s="9"/>
-      <c r="I25" s="9"/>
-    </row>
-    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="I25" s="10"/>
+    </row>
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D26" s="10"/>
-      <c r="I26" s="9"/>
-    </row>
-    <row r="27" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D27" s="9"/>
-      <c r="I27" s="10"/>
-    </row>
-    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="D28" s="10"/>
-    </row>
-    <row r="29" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="4:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="G29" s="10"/>
+      <c r="I29" s="9"/>
+    </row>
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I30" s="9"/>
     </row>
-    <row r="31" spans="4:9" x14ac:dyDescent="0.3">
-      <c r="G31" s="10"/>
-      <c r="I31" s="9"/>
-    </row>
-    <row r="32" spans="4:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="I31" s="10"/>
+    </row>
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
       <c r="I32" s="9"/>
     </row>
-    <row r="33" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I33" s="10"/>
     </row>
-    <row r="34" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I34" s="9"/>
-    </row>
-    <row r="35" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I35" s="10"/>
-    </row>
-    <row r="37" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I35" s="9"/>
+    </row>
+    <row r="36" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I36" s="9"/>
+    </row>
+    <row r="37" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I38" s="9"/>
     </row>
-    <row r="39" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I39" s="9"/>
     </row>
-    <row r="40" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I40" s="9"/>
-    </row>
-    <row r="41" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I41" s="9"/>
-    </row>
-    <row r="42" spans="9:9" x14ac:dyDescent="0.3">
-      <c r="I42" s="10"/>
+    <row r="40" spans="9:9" x14ac:dyDescent="0.25">
+      <c r="I40" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -861,12 +781,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CAD0B7-4C47-44E3-ACD2-2B082261F449}">
   <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="32.5546875" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,7 +815,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -924,12 +844,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="D3" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>8</v>
       </c>
@@ -952,7 +872,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -981,7 +901,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
@@ -1004,32 +924,32 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H14" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H15" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="H16" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H17" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H18" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +981,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -1079,7 +999,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2</v>
       </c>
@@ -1090,7 +1010,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3</v>
       </c>
@@ -1122,7 +1042,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>4</v>
       </c>
@@ -1154,7 +1074,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>5</v>
       </c>
@@ -1194,9 +1114,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D340067D-92C5-4A87-863D-4C9C26FE9C40}">
   <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1228,7 +1148,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1246,7 +1166,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1257,7 +1177,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1289,7 +1209,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1321,7 +1241,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1353,7 +1273,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1367,7 +1287,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1402,7 +1322,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
@@ -1437,7 +1357,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>5</v>
       </c>
